--- a/SaidaRPA/Excel/status-indicador_01-02-2026_28-02-2026.xlsx
+++ b/SaidaRPA/Excel/status-indicador_01-02-2026_28-02-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -531,11 +531,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -551,22 +551,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CEA</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -591,11 +591,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -606,16 +606,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -631,17 +631,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Análise</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -706,47 +706,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Rechamadas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rechamadas</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -766,7 +766,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -786,7 +786,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -795,18 +795,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -815,33 +815,33 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -866,7 +866,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -951,131 +951,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Novo</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Análise</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
         <v>13</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
